--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:58</t>
+    <t xml:space="preserve">2026-09-10 01:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:09</t>
+    <t xml:space="preserve">2026-09-12 22:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:21</t>
+    <t xml:space="preserve">2026-09-23 23:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:50</t>
+    <t xml:space="preserve">2026-10-02 16:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:00</t>
+    <t xml:space="preserve">2026-10-04 10:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:30</t>
+    <t xml:space="preserve">2026-10-05 15:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
